--- a/finance/_refresh_four-seasons.xlsx
+++ b/finance/_refresh_four-seasons.xlsx
@@ -1241,7 +1241,7 @@
       </c>
       <c r="F19" s="14" t="inlineStr">
         <is>
-          <t>Cap on revenue sailings/day — MID headline duty cycle; thin=12 / full=18 bookends in _utilization_scenarios (Jaideep 2026-06-21).</t>
+          <t>Cap on revenue sailings/day — 15 across thin/mid/full scenarios (Jaideep 2026-06-21).</t>
         </is>
       </c>
     </row>
@@ -1554,7 +1554,7 @@
         <v>0.7</v>
       </c>
       <c r="C33" s="19" t="n">
-        <v>0.85</v>
+        <v>0.75</v>
       </c>
       <c r="F33" s="14" t="inlineStr">
         <is>

--- a/finance/_refresh_four-seasons.xlsx
+++ b/finance/_refresh_four-seasons.xlsx
@@ -27,23 +27,23 @@
     <definedName name="dwell_min">'Assumptions'!$B$18</definedName>
     <definedName name="max_tpd">'Assumptions'!$B$19</definedName>
     <definedName name="crew_factor">'Assumptions'!$B$20</definedName>
-    <definedName name="ins_pct">'Assumptions'!$B$21</definedName>
-    <definedName name="charge_berth">'Assumptions'!$B$22</definedName>
-    <definedName name="mech_uptime">'Assumptions'!$B$23</definedName>
-    <definedName name="capture">'Assumptions'!$B$24</definedName>
-    <definedName name="capture_captive">'Assumptions'!$B$25</definedName>
-    <definedName name="discount">'Assumptions'!$B$26</definedName>
-    <definedName name="diesel_co2pg">'Assumptions'!$B$27</definedName>
-    <definedName name="load_thin">'Assumptions'!$B$31</definedName>
-    <definedName name="revleg_thin">'Assumptions'!$C$31</definedName>
-    <definedName name="load_mid">'Assumptions'!$B$32</definedName>
-    <definedName name="revleg_mid">'Assumptions'!$C$32</definedName>
-    <definedName name="load_full">'Assumptions'!$B$33</definedName>
-    <definedName name="revleg_full">'Assumptions'!$C$33</definedName>
-    <definedName name="band_tbl">'Assumptions'!$A$31:$C$33</definedName>
-    <definedName name="scenario">'Assumptions'!$B$35</definedName>
-    <definedName name="load_sel">'Assumptions'!$B$36</definedName>
-    <definedName name="revleg_sel">'Assumptions'!$B$37</definedName>
+    <definedName name="mech_uptime">'Assumptions'!$B$21</definedName>
+    <definedName name="capture">'Assumptions'!$B$22</definedName>
+    <definedName name="capture_captive">'Assumptions'!$B$23</definedName>
+    <definedName name="discount">'Assumptions'!$B$24</definedName>
+    <definedName name="diesel_co2pg">'Assumptions'!$B$25</definedName>
+    <definedName name="ins_pct">'Assumptions'!$B$29</definedName>
+    <definedName name="charge_berth">'Assumptions'!$B$30</definedName>
+    <definedName name="load_thin">'Assumptions'!$B$34</definedName>
+    <definedName name="revleg_thin">'Assumptions'!$C$34</definedName>
+    <definedName name="load_mid">'Assumptions'!$B$35</definedName>
+    <definedName name="revleg_mid">'Assumptions'!$C$35</definedName>
+    <definedName name="load_full">'Assumptions'!$B$36</definedName>
+    <definedName name="revleg_full">'Assumptions'!$C$36</definedName>
+    <definedName name="band_tbl">'Assumptions'!$A$34:$C$36</definedName>
+    <definedName name="scenario">'Assumptions'!$B$38</definedName>
+    <definedName name="load_sel">'Assumptions'!$B$39</definedName>
+    <definedName name="revleg_sel">'Assumptions'!$B$40</definedName>
     <definedName name="country_opex">'Country opex'!$A$4:$G$3</definedName>
     <definedName name="som_floor_fleet">'Corridor economics'!$D$8</definedName>
     <definedName name="som_floor_rev">'Corridor economics'!$E$8</definedName>
@@ -616,7 +616,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="B2:B27"/>
+  <dimension ref="B2:B36"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="3" customWidth="1" min="1" max="1"/>
@@ -695,84 +695,143 @@
     <row r="14">
       <c r="B14" s="4" t="inlineStr">
         <is>
-          <t>EBITDA  = REVENUE − OPEX   (energy + captain + marina/overhead + maintenance)</t>
+          <t>EBITDA  = REVENUE − OPEX</t>
         </is>
       </c>
     </row>
     <row r="15">
-      <c r="B15" s="4" t="inlineStr">
+      <c r="B15" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">    OPEX = energy + crew + berth/port admin + maintenance + vessel insurance + fast-charge berth</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="B16" s="4" t="inlineStr">
         <is>
           <t>PAYBACK = vessel CAPEX ÷ EBITDA</t>
         </is>
       </c>
     </row>
-    <row r="16">
-      <c r="B16" s="2" t="inlineStr"/>
-    </row>
     <row r="17">
-      <c r="B17" s="3" t="inlineStr">
-        <is>
-          <t>From demand pool to fleet &amp; market size</t>
-        </is>
-      </c>
+      <c r="B17" s="2" t="inlineStr"/>
     </row>
     <row r="18">
-      <c r="B18" s="5" t="inlineStr">
-        <is>
-          <t>Navier serviceable rides/yr = corridor demand pool × capture rate (10% on contested corridors; ~90% on captive sole-operator transfer legs — see the per-row Capture % column)</t>
+      <c r="B18" s="3" t="inlineStr">
+        <is>
+          <t>OPEX lines (per boat, per year — no double-counting)</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="B19" s="2" t="inlineStr">
         <is>
-          <t>Vessels supported = FLOOR(Navier rides/yr ÷ pax/yr per boat);  Market rev = vessels × rev/boat. The 'Market sizing' tab rolls these up into the SOM → SAM → TAM ladder.</t>
+          <t>Energy — variable propulsion cost: kWh on revenue sailings × local $/kWh (Country opex tab). Excludes utility demand charges.</t>
         </is>
       </c>
     </row>
     <row r="20">
-      <c r="B20" s="2" t="inlineStr"/>
+      <c r="B20" s="2" t="inlineStr">
+        <is>
+          <t>Crew — fully-loaded captain + relief: local captain wage × crew FTE factor (Country opex + Assumptions).</t>
+        </is>
+      </c>
     </row>
     <row r="21">
-      <c r="B21" s="3" t="inlineStr">
-        <is>
-          <t>The scenario toggle (what we flex)</t>
+      <c r="B21" s="2" t="inlineStr">
+        <is>
+          <t>Berth &amp; port admin — fixed annual berth, port fees, and local marine admin (Country opex tab). Excludes vessel H&amp;M+P&amp;I and fast-charge infrastructure.</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="B22" s="2" t="inlineStr">
         <is>
-          <t>'Corridor economics' has a SCENARIO cell = THIN / MID / FULL. It flexes two levers: load factor (how full the boat is) and revenue-leg factor (how many legs earn full fare). MID is the headline. Change that one cell and the whole model recomputes. The right-hand Payback THIN/MID/FULL columns always show all three at once.</t>
+          <t>Maintenance — vessel annual maintenance reserve (Assumptions tab).</t>
         </is>
       </c>
     </row>
     <row r="23">
-      <c r="B23" s="2" t="inlineStr"/>
+      <c r="B23" s="2" t="inlineStr">
+        <is>
+          <t>Vessel insurance — commercial H&amp;M + P&amp;I as % of regional CAPEX (Assumptions % × Country opex CAPEX column).</t>
+        </is>
+      </c>
     </row>
     <row r="24">
-      <c r="B24" s="3" t="inlineStr">
+      <c r="B24" s="2" t="inlineStr">
+        <is>
+          <t>Fast-charge berth — dedicated fast-charge berth slot + utility demand charges (Assumptions default; overridable per market). Separate from per-kWh energy and berth/port admin.</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="B25" s="2" t="inlineStr"/>
+    </row>
+    <row r="26">
+      <c r="B26" s="3" t="inlineStr">
+        <is>
+          <t>From demand pool to fleet &amp; market size</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="B27" s="5" t="inlineStr">
+        <is>
+          <t>Navier serviceable rides/yr = corridor demand pool × capture rate (10% on contested corridors; ~90% on captive sole-operator transfer legs — see the per-row Capture % column)</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="B28" s="2" t="inlineStr">
+        <is>
+          <t>Vessels supported = FLOOR(Navier rides/yr ÷ pax/yr per boat);  Market rev = vessels × rev/boat. The 'Market sizing' tab rolls these up into the SOM → SAM → TAM ladder.</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="B29" s="2" t="inlineStr"/>
+    </row>
+    <row r="30">
+      <c r="B30" s="3" t="inlineStr">
+        <is>
+          <t>The scenario toggle (what we flex)</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="B31" s="2" t="inlineStr">
+        <is>
+          <t>'Corridor economics' has a SCENARIO cell = THIN / MID / FULL. It flexes load factor (occupancy) and revenue-leg factor (share of legs that earn full fare). Max trips/day is fixed across all three bands (see Assumptions). MID is the headline. Change SCENARIO and the whole model recomputes. Payback THIN/MID/FULL columns always show all three at once.</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="B32" s="2" t="inlineStr"/>
+    </row>
+    <row r="33">
+      <c r="B33" s="3" t="inlineStr">
         <is>
           <t>Colour &amp; provenance legend</t>
         </is>
       </c>
     </row>
-    <row r="25">
-      <c r="B25" s="6" t="inlineStr">
+    <row r="34">
+      <c r="B34" s="6" t="inlineStr">
         <is>
           <t xml:space="preserve">   Yellow = INPUTS you can change (fare, distance, demand, weather).</t>
         </is>
       </c>
     </row>
-    <row r="26">
-      <c r="B26" s="7" t="inlineStr">
+    <row r="35">
+      <c r="B35" s="7" t="inlineStr">
         <is>
           <t xml:space="preserve">   Green  = COMPUTED by formula.</t>
         </is>
       </c>
     </row>
-    <row r="27">
-      <c r="B27" s="2" t="inlineStr">
+    <row r="36">
+      <c r="B36" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">   Every fare &amp; demand figure carries a Source tier (T1 official → T5 modeled) + Confidence (high/med/low). Null beats a wrong number: no published pool → blank, not a guess.</t>
         </is>
@@ -789,7 +848,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F37"/>
+  <dimension ref="A1:F40"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="30" customWidth="1" min="1" max="1"/>
@@ -1278,11 +1337,11 @@
     <row r="21">
       <c r="A21" s="11" t="inlineStr">
         <is>
-          <t>Insurance (% of capex/yr)</t>
+          <t>Mechanical uptime</t>
         </is>
       </c>
       <c r="B21" s="17" t="n">
-        <v>0.025</v>
+        <v>0.75</v>
       </c>
       <c r="C21" s="13" t="inlineStr">
         <is>
@@ -1291,7 +1350,7 @@
       </c>
       <c r="D21" s="13" t="inlineStr">
         <is>
-          <t>T3</t>
+          <t>T4</t>
         </is>
       </c>
       <c r="E21" s="13" t="inlineStr">
@@ -1301,29 +1360,25 @@
       </c>
       <c r="F21" s="14" t="inlineStr">
         <is>
-          <t>H&amp;M + P&amp;I for a commercial passenger vessel ~2.5%/yr of capex; scales with regional capex overrides (Jaideep 2026-06-19).</t>
+          <t>Blade luxury aviation ~75-80% reliability uptime</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" s="11" t="inlineStr">
         <is>
-          <t>Charging &amp; berth (additional to marina+energy)</t>
-        </is>
-      </c>
-      <c r="B22" s="15" t="n">
-        <v>18000</v>
+          <t>Navier capture rate</t>
+        </is>
+      </c>
+      <c r="B22" s="17" t="n">
+        <v>0.1</v>
       </c>
       <c r="C22" s="13" t="inlineStr">
         <is>
-          <t>USD/yr</t>
-        </is>
-      </c>
-      <c r="D22" s="13" t="inlineStr">
-        <is>
-          <t>T3</t>
-        </is>
-      </c>
+          <t>frac</t>
+        </is>
+      </c>
+      <c r="D22" s="13" t="inlineStr"/>
       <c r="E22" s="13" t="inlineStr">
         <is>
           <t>med</t>
@@ -1331,29 +1386,25 @@
       </c>
       <c r="F22" s="14" t="inlineStr">
         <is>
-          <t>Dedicated fast-charge berth + demand charges, ADDITIONAL to marina overhead and energy (Jaideep 2026-06-19). L3-overridable.</t>
+          <t>Navier wins ~10% of a CONTESTED corridor demand pool (locked). Captive sole-operator transfer legs (captive:true / luxury_charter / hospitality archetypes) carry the captive rate instead — see per-row Capture %.</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" s="11" t="inlineStr">
         <is>
-          <t>Mechanical uptime</t>
+          <t>Captive capture rate (A′ corridors)</t>
         </is>
       </c>
       <c r="B23" s="17" t="n">
-        <v>0.75</v>
+        <v>0.9</v>
       </c>
       <c r="C23" s="13" t="inlineStr">
         <is>
           <t>frac</t>
         </is>
       </c>
-      <c r="D23" s="13" t="inlineStr">
-        <is>
-          <t>T4</t>
-        </is>
-      </c>
+      <c r="D23" s="13" t="inlineStr"/>
       <c r="E23" s="13" t="inlineStr">
         <is>
           <t>med</t>
@@ -1361,255 +1412,303 @@
       </c>
       <c r="F23" s="14" t="inlineStr">
         <is>
-          <t>Blade luxury aviation ~75-80% reliability uptime</t>
+          <t>Sole-operator water-access-only transfer legs (captive:true or luxury_charter/hospitality archetype): Navier IS the transfer fleet — capture ~90%. Applied per-row in the Capture % column.</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" s="11" t="inlineStr">
         <is>
-          <t>Navier capture rate</t>
-        </is>
-      </c>
-      <c r="B24" s="17" t="n">
-        <v>0.1</v>
+          <t>Discount factor (vs comparable fare)</t>
+        </is>
+      </c>
+      <c r="B24" s="16" t="n">
+        <v>1</v>
       </c>
       <c r="C24" s="13" t="inlineStr">
         <is>
           <t>frac</t>
         </is>
       </c>
-      <c r="D24" s="13" t="inlineStr"/>
+      <c r="D24" s="13" t="inlineStr">
+        <is>
+          <t>T1</t>
+        </is>
+      </c>
       <c r="E24" s="13" t="inlineStr">
         <is>
-          <t>med</t>
+          <t>high</t>
         </is>
       </c>
       <c r="F24" s="14" t="inlineStr">
         <is>
-          <t>Navier wins ~10% of a CONTESTED corridor demand pool (locked). Captive sole-operator transfer legs (captive:true / luxury_charter / hospitality archetypes) carry the captive rate instead — see per-row Capture %.</t>
+          <t>Market parity — better product, not cheaper (locked).</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" s="11" t="inlineStr">
         <is>
-          <t>Captive capture rate (A′ corridors)</t>
-        </is>
-      </c>
-      <c r="B25" s="17" t="n">
-        <v>0.9</v>
+          <t>Diesel CO₂ per gallon</t>
+        </is>
+      </c>
+      <c r="B25" s="16" t="n">
+        <v>10.21</v>
       </c>
       <c r="C25" s="13" t="inlineStr">
         <is>
+          <t>kg/gal</t>
+        </is>
+      </c>
+      <c r="D25" s="13" t="inlineStr">
+        <is>
+          <t>T1</t>
+        </is>
+      </c>
+      <c r="E25" s="13" t="inlineStr">
+        <is>
+          <t>high</t>
+        </is>
+      </c>
+      <c r="F25" s="14" t="inlineStr">
+        <is>
+          <t>US EPA: 10.21 kg CO2 per gallon marine/diesel</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" s="9" t="inlineStr">
+        <is>
+          <t>OPEX defaults  (global fallbacks — localized energy, crew, berth admin on Country opex tab)</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" s="10" t="inlineStr">
+        <is>
+          <t>Parameter</t>
+        </is>
+      </c>
+      <c r="B28" s="10" t="inlineStr">
+        <is>
+          <t>Value</t>
+        </is>
+      </c>
+      <c r="C28" s="10" t="inlineStr">
+        <is>
+          <t>Unit</t>
+        </is>
+      </c>
+      <c r="D28" s="10" t="inlineStr">
+        <is>
+          <t>Tier</t>
+        </is>
+      </c>
+      <c r="E28" s="10" t="inlineStr">
+        <is>
+          <t>Conf.</t>
+        </is>
+      </c>
+      <c r="F28" s="10" t="inlineStr">
+        <is>
+          <t>Source / note</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" s="11" t="inlineStr">
+        <is>
+          <t>Vessel insurance — H&amp;M + P&amp;I (% of CAPEX/yr)</t>
+        </is>
+      </c>
+      <c r="B29" s="17" t="n">
+        <v>0.025</v>
+      </c>
+      <c r="C29" s="13" t="inlineStr">
+        <is>
           <t>frac</t>
         </is>
       </c>
-      <c r="D25" s="13" t="inlineStr"/>
-      <c r="E25" s="13" t="inlineStr">
+      <c r="D29" s="13" t="inlineStr">
+        <is>
+          <t>T3</t>
+        </is>
+      </c>
+      <c r="E29" s="13" t="inlineStr">
         <is>
           <t>med</t>
         </is>
       </c>
-      <c r="F25" s="14" t="inlineStr">
-        <is>
-          <t>Sole-operator water-access-only transfer legs (captive:true or luxury_charter/hospitality archetype): Navier IS the transfer fleet — capture ~90%. Applied per-row in the Capture % column.</t>
-        </is>
-      </c>
-    </row>
-    <row r="26">
-      <c r="A26" s="11" t="inlineStr">
-        <is>
-          <t>Discount factor (vs comparable fare)</t>
-        </is>
-      </c>
-      <c r="B26" s="16" t="n">
-        <v>1</v>
-      </c>
-      <c r="C26" s="13" t="inlineStr">
-        <is>
-          <t>frac</t>
-        </is>
-      </c>
-      <c r="D26" s="13" t="inlineStr">
-        <is>
-          <t>T1</t>
-        </is>
-      </c>
-      <c r="E26" s="13" t="inlineStr">
-        <is>
-          <t>high</t>
-        </is>
-      </c>
-      <c r="F26" s="14" t="inlineStr">
-        <is>
-          <t>Market parity — better product, not cheaper (locked).</t>
-        </is>
-      </c>
-    </row>
-    <row r="27">
-      <c r="A27" s="11" t="inlineStr">
-        <is>
-          <t>Diesel CO₂ per gallon</t>
-        </is>
-      </c>
-      <c r="B27" s="16" t="n">
-        <v>10.21</v>
-      </c>
-      <c r="C27" s="13" t="inlineStr">
-        <is>
-          <t>kg/gal</t>
-        </is>
-      </c>
-      <c r="D27" s="13" t="inlineStr">
-        <is>
-          <t>T1</t>
-        </is>
-      </c>
-      <c r="E27" s="13" t="inlineStr">
-        <is>
-          <t>high</t>
-        </is>
-      </c>
-      <c r="F27" s="14" t="inlineStr">
-        <is>
-          <t>US EPA: 10.21 kg CO2 per gallon marine/diesel</t>
-        </is>
-      </c>
-    </row>
-    <row r="29">
-      <c r="A29" s="9" t="inlineStr">
-        <is>
-          <t>Utilization scenarios  (the two levers we flex)</t>
+      <c r="F29" s="14" t="inlineStr">
+        <is>
+          <t>Commercial vessel H&amp;M + P&amp;I ~2.5%/yr of regional CAPEX. Separate from berth/port admin in Country opex (Jaideep 2026-06-19).. Multiplied by regional CAPEX (Country opex col G). Not included in berth/port admin.</t>
         </is>
       </c>
     </row>
     <row r="30">
-      <c r="A30" s="10" t="inlineStr">
+      <c r="A30" s="11" t="inlineStr">
+        <is>
+          <t>Fast-charge berth &amp; demand charges (global default)</t>
+        </is>
+      </c>
+      <c r="B30" s="15" t="n">
+        <v>18000</v>
+      </c>
+      <c r="C30" s="13" t="inlineStr">
+        <is>
+          <t>USD/yr</t>
+        </is>
+      </c>
+      <c r="D30" s="13" t="inlineStr">
+        <is>
+          <t>T3</t>
+        </is>
+      </c>
+      <c r="E30" s="13" t="inlineStr">
+        <is>
+          <t>med</t>
+        </is>
+      </c>
+      <c r="F30" s="14" t="inlineStr">
+        <is>
+          <t>Dedicated fast-charge berth slot + utility demand charges. Excludes per-kWh propulsion energy and berth/port admin (Jaideep 2026-06-19). L3-overridable per market.. Dedicated charge berth + utility demand charges. Excludes per-kWh propulsion energy and berth/port admin. L3-overridable per market.</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" s="9" t="inlineStr">
+        <is>
+          <t>Utilization scenarios  (load factor + revenue-leg factor)</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" s="10" t="inlineStr">
         <is>
           <t>Scenario</t>
         </is>
       </c>
-      <c r="B30" s="10" t="inlineStr">
+      <c r="B33" s="10" t="inlineStr">
         <is>
           <t>Load factor</t>
         </is>
       </c>
-      <c r="C30" s="10" t="inlineStr">
+      <c r="C33" s="10" t="inlineStr">
         <is>
           <t>Rev-leg factor</t>
         </is>
       </c>
-      <c r="D30" s="10" t="inlineStr"/>
-      <c r="E30" s="10" t="inlineStr"/>
-      <c r="F30" s="10" t="inlineStr">
+      <c r="D33" s="10" t="inlineStr"/>
+      <c r="E33" s="10" t="inlineStr"/>
+      <c r="F33" s="10" t="inlineStr">
         <is>
           <t>Note</t>
         </is>
       </c>
     </row>
-    <row r="31">
-      <c r="A31" s="18" t="inlineStr">
+    <row r="34">
+      <c r="A34" s="18" t="inlineStr">
         <is>
           <t>THIN</t>
         </is>
       </c>
-      <c r="B31" s="19" t="n">
+      <c r="B34" s="19" t="n">
         <v>0.45</v>
       </c>
-      <c r="C31" s="19" t="n">
+      <c r="C34" s="19" t="n">
         <v>0.55</v>
       </c>
-      <c r="F31" s="14" t="inlineStr">
+      <c r="F34" s="14" t="inlineStr">
         <is>
           <t>thin/one-way/seasonal corridor — conservative floor</t>
         </is>
       </c>
     </row>
-    <row r="32">
-      <c r="A32" s="18" t="inlineStr">
+    <row r="35">
+      <c r="A35" s="18" t="inlineStr">
         <is>
           <t>MID</t>
         </is>
       </c>
-      <c r="B32" s="19" t="n">
+      <c r="B35" s="19" t="n">
         <v>0.55</v>
       </c>
-      <c r="C32" s="19" t="n">
+      <c r="C35" s="19" t="n">
         <v>0.65</v>
       </c>
-      <c r="F32" s="14" t="inlineStr">
+      <c r="F35" s="14" t="inlineStr">
         <is>
           <t>HEADLINE — realistic busy two-way corridor</t>
         </is>
       </c>
     </row>
-    <row r="33">
-      <c r="A33" s="18" t="inlineStr">
+    <row r="36">
+      <c r="A36" s="18" t="inlineStr">
         <is>
           <t>FULL</t>
         </is>
       </c>
-      <c r="B33" s="19" t="n">
+      <c r="B36" s="19" t="n">
         <v>0.7</v>
       </c>
-      <c r="C33" s="19" t="n">
+      <c r="C36" s="19" t="n">
         <v>0.75</v>
       </c>
-      <c r="F33" s="14" t="inlineStr">
+      <c r="F36" s="14" t="inlineStr">
         <is>
           <t>mature/dense corridor — optimistic ceiling</t>
         </is>
       </c>
     </row>
-    <row r="35">
-      <c r="A35" s="20" t="inlineStr">
+    <row r="38">
+      <c r="A38" s="20" t="inlineStr">
         <is>
           <t>SCENARIO (toggle me)</t>
         </is>
       </c>
-      <c r="B35" s="21" t="inlineStr">
+      <c r="B38" s="21" t="inlineStr">
         <is>
           <t>MID</t>
         </is>
       </c>
-      <c r="C35" s="22" t="inlineStr">
+      <c r="C38" s="22" t="inlineStr">
         <is>
           <t>← set THIN / MID / FULL</t>
         </is>
       </c>
     </row>
-    <row r="36">
-      <c r="A36" s="11" t="inlineStr">
+    <row r="39">
+      <c r="A39" s="11" t="inlineStr">
         <is>
           <t>Selected load factor</t>
         </is>
       </c>
-      <c r="B36" s="23">
-        <f>VLOOKUP(scenario,'Assumptions'!$A$31:$C$33,2,FALSE)</f>
-        <v/>
-      </c>
-    </row>
-    <row r="37">
-      <c r="A37" s="11" t="inlineStr">
+      <c r="B39" s="23">
+        <f>VLOOKUP(scenario,'Assumptions'!$A$34:$C$36,2,FALSE)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" s="11" t="inlineStr">
         <is>
           <t>Selected rev-leg factor</t>
         </is>
       </c>
-      <c r="B37" s="23">
-        <f>VLOOKUP(scenario,'Assumptions'!$A$31:$C$33,3,FALSE)</f>
+      <c r="B40" s="23">
+        <f>VLOOKUP(scenario,'Assumptions'!$A$34:$C$36,3,FALSE)</f>
         <v/>
       </c>
     </row>
   </sheetData>
-  <mergeCells count="4">
-    <mergeCell ref="A3:F3"/>
+  <mergeCells count="5">
     <mergeCell ref="A14:F14"/>
     <mergeCell ref="A1:F1"/>
-    <mergeCell ref="A29:F29"/>
+    <mergeCell ref="A32:F32"/>
+    <mergeCell ref="A27:F27"/>
+    <mergeCell ref="A3:F3"/>
   </mergeCells>
   <dataValidations count="1">
-    <dataValidation sqref="B35" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="0" type="list">
+    <dataValidation sqref="B38" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="0" type="list">
       <formula1>"THIN,MID,FULL"</formula1>
     </dataValidation>
   </dataValidations>
@@ -1639,7 +1738,7 @@
     <row r="1">
       <c r="A1" s="8" t="inlineStr">
         <is>
-          <t>Country opex — L3 localized layer (VLOOKUP target for the engine)</t>
+          <t>Country opex — localized inputs (crew, energy, berth admin, CAPEX)</t>
         </is>
       </c>
     </row>
@@ -1666,7 +1765,7 @@
       </c>
       <c r="E3" s="24" t="inlineStr">
         <is>
-          <t>Marina $/yr</t>
+          <t>Berth &amp; port admin $/yr</t>
         </is>
       </c>
       <c r="F3" s="24" t="inlineStr">
@@ -1681,7 +1780,7 @@
       </c>
       <c r="H3" s="24" t="inlineStr">
         <is>
-          <t>Source notes (captain | energy | marina)</t>
+          <t>Source notes (crew | energy | berth admin)</t>
         </is>
       </c>
     </row>
@@ -1724,10 +1823,10 @@
     <col width="11" customWidth="1" min="20" max="20"/>
     <col width="10" customWidth="1" min="21" max="21"/>
     <col width="10" customWidth="1" min="22" max="22"/>
-    <col width="10" customWidth="1" min="23" max="23"/>
+    <col width="12" customWidth="1" min="23" max="23"/>
     <col width="9" customWidth="1" min="24" max="24"/>
-    <col width="10" customWidth="1" min="25" max="25"/>
-    <col width="11" customWidth="1" min="26" max="26"/>
+    <col width="12" customWidth="1" min="25" max="25"/>
+    <col width="12" customWidth="1" min="26" max="26"/>
     <col width="11" customWidth="1" min="27" max="27"/>
     <col width="10" customWidth="1" min="28" max="28"/>
     <col width="11" customWidth="1" min="29" max="29"/>
@@ -1888,7 +1987,7 @@
       </c>
       <c r="W3" s="24" t="inlineStr">
         <is>
-          <t>Marina/yr</t>
+          <t>Berth &amp; port admin/yr</t>
         </is>
       </c>
       <c r="X3" s="24" t="inlineStr">
@@ -1898,12 +1997,12 @@
       </c>
       <c r="Y3" s="24" t="inlineStr">
         <is>
-          <t>Insurance/yr</t>
+          <t>Vessel insurance/yr</t>
         </is>
       </c>
       <c r="Z3" s="24" t="inlineStr">
         <is>
-          <t>Charge+berth/yr</t>
+          <t>Fast-charge berth/yr</t>
         </is>
       </c>
       <c r="AA3" s="24" t="inlineStr">

--- a/finance/_refresh_four-seasons.xlsx
+++ b/finance/_refresh_four-seasons.xlsx
@@ -44,9 +44,9 @@
     <definedName name="scenario">'Assumptions'!$B$38</definedName>
     <definedName name="load_sel">'Assumptions'!$B$39</definedName>
     <definedName name="revleg_sel">'Assumptions'!$B$40</definedName>
-    <definedName name="country_opex">'Country opex'!$A$4:$G$3</definedName>
-    <definedName name="som_floor_fleet">'Corridor economics'!$D$8</definedName>
-    <definedName name="som_floor_rev">'Corridor economics'!$E$8</definedName>
+    <definedName name="country_opex">'Country opex'!$A$4:$G$4</definedName>
+    <definedName name="som_floor_fleet">'Corridor economics'!$D$11</definedName>
+    <definedName name="som_floor_rev">'Corridor economics'!$E$11</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -54,11 +54,13 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="2">
+  <numFmts count="4">
     <numFmt numFmtId="164" formatCode="&quot;$&quot;#,##0"/>
     <numFmt numFmtId="165" formatCode="0.0%"/>
+    <numFmt numFmtId="166" formatCode="&quot;$&quot;#,##0.00"/>
+    <numFmt numFmtId="167" formatCode="#,##0.0"/>
   </numFmts>
-  <fonts count="8">
+  <fonts count="11">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -96,8 +98,19 @@
       <b val="1"/>
       <sz val="12"/>
     </font>
+    <font>
+      <sz val="9"/>
+    </font>
+    <font>
+      <color rgb="00555555"/>
+      <sz val="8"/>
+    </font>
+    <font>
+      <color rgb="009C4500"/>
+      <sz val="8"/>
+    </font>
   </fonts>
-  <fills count="8">
+  <fills count="9">
     <fill>
       <patternFill/>
     </fill>
@@ -134,6 +147,11 @@
         <fgColor rgb="00FCE4D6"/>
       </patternFill>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00F2F2F2"/>
+      </patternFill>
+    </fill>
   </fills>
   <borders count="2">
     <border>
@@ -161,7 +179,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="35">
+  <cellXfs count="55">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="center"/>
@@ -227,8 +245,61 @@
     <xf numFmtId="0" fontId="5" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="164" fontId="0" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="166" fontId="0" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="4" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="8" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="3" fontId="0" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="167" fontId="8" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="3" fontId="8" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="165" fontId="8" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="4" fontId="8" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="166" fontId="8" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="164" fontId="8" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="165" fontId="0" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="3" fontId="6" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="4" fontId="8" fillId="7" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="8" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="3" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="164" fontId="2" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
@@ -240,11 +311,16 @@
     <xf numFmtId="3" fontId="2" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="165" fontId="0" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="3" fontId="0" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="164" fontId="0" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="3" fontId="2" fillId="7" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="164" fontId="2" fillId="7" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
@@ -998,11 +1074,11 @@
     <row r="8">
       <c r="A8" s="11" t="inlineStr">
         <is>
-          <t>CAPEX (per vessel; US/EU base — ROW=$600K, see Country opex tab col G)</t>
+          <t>CAPEX (per vessel; hospitality N30 list = $1M, region-independent — see Country opex tab col G)</t>
         </is>
       </c>
       <c r="B8" s="15" t="n">
-        <v>900000</v>
+        <v>1000000</v>
       </c>
       <c r="C8" s="13" t="inlineStr">
         <is>
@@ -1722,7 +1798,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H3"/>
+  <dimension ref="A1:H4"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="18" customWidth="1" min="1" max="1"/>
@@ -1784,6 +1860,36 @@
         </is>
       </c>
     </row>
+    <row r="4">
+      <c r="A4" s="25" t="inlineStr">
+        <is>
+          <t>Maldives</t>
+        </is>
+      </c>
+      <c r="B4" s="26" t="n">
+        <v>27000</v>
+      </c>
+      <c r="C4" s="27" t="n">
+        <v>0.3</v>
+      </c>
+      <c r="D4" s="19" t="n">
+        <v>0.72</v>
+      </c>
+      <c r="E4" s="26" t="n">
+        <v>16000</v>
+      </c>
+      <c r="F4" s="19" t="n">
+        <v>0.63</v>
+      </c>
+      <c r="G4" s="26" t="n">
+        <v>1000000</v>
+      </c>
+      <c r="H4" s="14" t="inlineStr">
+        <is>
+          <t>Maldives resort/tourism marine crew (real 2026 job listings): MHLZ speedboat captain MVR 15,000 + MVR 3,000 food allowance = MVR 18k/mo; jobcenter.mv boat captain MVR 20,000-25,000 + service charge; expat safari/yacht captains EUR 3,200/mo (high-side). Blended 1 resort speedboat captain (~MVR 15-20k base + service charge/food ~$1,500-1,700/mo all-in) + deckhand (~MVR 10-12k all-in ~$700/mo) fully-loaded ~$2,250/mo = ~$27k/vessel/yr @MVR 15.42. Higher than SEA (service-charge system + some expat crew); between Thailand $24k and GCC $36-42k. | Maldives has among the HIGHEST electricity costs in South Asia (near-100% imported diesel). STELCO Male' commercial tariff MVR 3.30/kWh = $0.214 (stelco.com.mv tariff-rates). Resort islands SELF-GENERATE on diesel gensets at $0.30-0.40/kWh (CIF SREP: diesel $0.35/kWh; World Bank 30-40 US-cents on larger islands; ADB/Climate Policy Radar efficient-diesel $0.23-0.33). Charging an electric tourism boat will largely occur at diesel-powered resort islands -&gt; anchored $0.30 (floor STELCO grid $0.214, ceiling resort diesel $0.40). Higher than Singapore $0.21. | Modeled berth+insurance+admin per vessel/yr. Maldives is a high-cost island operating environment (everything imported; no true marinas - resort jetties/anchorage + maintenance + marine insurance). Above Thailand $12k / Malaysia $11k, near Taiwan $14k, below Singapore $20k / GCC $18-22k. Tagged low. | CAPEX LB-260 hospitality N30 list = $1M (region-independent)</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <mergeCells count="1">
     <mergeCell ref="A1:H1"/>
@@ -1798,7 +1904,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AX8"/>
+  <dimension ref="A1:AY12"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
@@ -1843,14 +1949,15 @@
     <col width="9" customWidth="1" min="40" max="40"/>
     <col width="13" customWidth="1" min="41" max="41"/>
     <col width="26" customWidth="1" min="42" max="42"/>
-    <col width="16" customWidth="1" min="43" max="43"/>
+    <col width="14" customWidth="1" min="43" max="43"/>
     <col width="16" customWidth="1" min="44" max="44"/>
-    <col width="9" customWidth="1" min="45" max="45"/>
+    <col width="16" customWidth="1" min="45" max="45"/>
     <col width="9" customWidth="1" min="46" max="46"/>
     <col width="9" customWidth="1" min="47" max="47"/>
     <col width="9" customWidth="1" min="48" max="48"/>
-    <col width="50" customWidth="1" min="49" max="49"/>
+    <col width="9" customWidth="1" min="49" max="49"/>
     <col width="50" customWidth="1" min="50" max="50"/>
+    <col width="50" customWidth="1" min="51" max="51"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -1859,7 +1966,7 @@
           <t>Navier × Four-Seasons — Corridor economics (one boat, one year; MID = headline)</t>
         </is>
       </c>
-      <c r="N1" s="25" t="inlineStr">
+      <c r="N1" s="28" t="inlineStr">
         <is>
           <t>SCENARIO:</t>
         </is>
@@ -2087,124 +2194,562 @@
       </c>
       <c r="AQ3" s="24" t="inlineStr">
         <is>
+          <t>Floor bucket (aggregate status)</t>
+        </is>
+      </c>
+      <c r="AR3" s="24" t="inlineStr">
+        <is>
           <t>Forward SAM (2030-dated; held OUT of grounded floor)</t>
         </is>
       </c>
-      <c r="AR3" s="24" t="inlineStr">
+      <c r="AS3" s="24" t="inlineStr">
         <is>
           <t>Upside tier (LB-99; held OUT of grounded floor)</t>
         </is>
       </c>
-      <c r="AS3" s="24" t="inlineStr">
+      <c r="AT3" s="24" t="inlineStr">
         <is>
           <t>Fleet ceiling (captive villas/25)</t>
         </is>
       </c>
-      <c r="AT3" s="24" t="inlineStr">
+      <c r="AU3" s="24" t="inlineStr">
         <is>
           <t>Payback THIN</t>
         </is>
       </c>
-      <c r="AU3" s="24" t="inlineStr">
+      <c r="AV3" s="24" t="inlineStr">
         <is>
           <t>Payback MID</t>
         </is>
       </c>
-      <c r="AV3" s="24" t="inlineStr">
+      <c r="AW3" s="24" t="inlineStr">
         <is>
           <t>Payback FULL</t>
         </is>
       </c>
-      <c r="AW3" s="24" t="inlineStr">
+      <c r="AX3" s="24" t="inlineStr">
         <is>
           <t>Fare source (provenance)</t>
         </is>
       </c>
-      <c r="AX3" s="24" t="inlineStr">
+      <c r="AY3" s="24" t="inlineStr">
         <is>
           <t>Demand source (provenance)</t>
         </is>
       </c>
     </row>
     <row r="4">
-      <c r="A4" s="26" t="inlineStr">
+      <c r="A4" s="29" t="inlineStr">
+        <is>
+          <t>Four Seasons</t>
+        </is>
+      </c>
+      <c r="B4" s="29" t="inlineStr">
+        <is>
+          <t>Maldives</t>
+        </is>
+      </c>
+      <c r="C4" s="30" t="inlineStr">
+        <is>
+          <t>Dharavandhoo Airport, Baa → Four Seasons Landaa Giraavaru (Baa)</t>
+        </is>
+      </c>
+      <c r="D4" s="31" t="n">
+        <v>9.5</v>
+      </c>
+      <c r="E4" s="26" t="n">
+        <v>200</v>
+      </c>
+      <c r="F4" s="32" t="inlineStr">
+        <is>
+          <t>T3</t>
+        </is>
+      </c>
+      <c r="G4" s="32" t="inlineStr">
+        <is>
+          <t>med</t>
+        </is>
+      </c>
+      <c r="H4" s="19" t="n">
+        <v>1</v>
+      </c>
+      <c r="I4" s="33">
+        <f>60*D4/cruise_kt</f>
+        <v/>
+      </c>
+      <c r="J4" s="33">
+        <f>I4+turn_min+dwell_min</f>
+        <v/>
+      </c>
+      <c r="K4" s="34">
+        <f>MIN(15,FLOOR(60*service_hr/J4,1))</f>
+        <v/>
+      </c>
+      <c r="L4" s="34">
+        <f>ROUND(365*mech_uptime*H4,0)</f>
+        <v/>
+      </c>
+      <c r="M4" s="35">
+        <f>mech_uptime</f>
+        <v/>
+      </c>
+      <c r="N4" s="35">
+        <f>revleg_sel</f>
+        <v/>
+      </c>
+      <c r="O4" s="34">
+        <f>ROUND(K4*L4*revleg_sel,0)</f>
+        <v/>
+      </c>
+      <c r="P4" s="36">
+        <f>load_sel</f>
+        <v/>
+      </c>
+      <c r="Q4" s="36">
+        <f>pax_cap*P4</f>
+        <v/>
+      </c>
+      <c r="R4" s="34">
+        <f>Q4*O4</f>
+        <v/>
+      </c>
+      <c r="S4" s="37">
+        <f>E4*discount</f>
+        <v/>
+      </c>
+      <c r="T4" s="38">
+        <f>S4*R4</f>
+        <v/>
+      </c>
+      <c r="U4" s="38">
+        <f>(battery/range_nm)*D4*O4*VLOOKUP(B4,country_opex,3,FALSE)</f>
+        <v/>
+      </c>
+      <c r="V4" s="38">
+        <f>VLOOKUP(B4,country_opex,2,FALSE)*crew_factor</f>
+        <v/>
+      </c>
+      <c r="W4" s="38">
+        <f>VLOOKUP(B4,country_opex,5,FALSE)</f>
+        <v/>
+      </c>
+      <c r="X4" s="38">
+        <f>maint</f>
+        <v/>
+      </c>
+      <c r="Y4" s="38">
+        <f>VLOOKUP(B4,country_opex,7,FALSE)*ins_pct</f>
+        <v/>
+      </c>
+      <c r="Z4" s="38">
+        <f>charge_berth</f>
+        <v/>
+      </c>
+      <c r="AA4" s="38">
+        <f>U4+V4+W4+X4+Y4+Z4</f>
+        <v/>
+      </c>
+      <c r="AB4" s="38">
+        <f>VLOOKUP(B4,country_opex,7,FALSE)/dep_years</f>
+        <v/>
+      </c>
+      <c r="AC4" s="38">
+        <f>T4-AA4</f>
+        <v/>
+      </c>
+      <c r="AD4" s="35">
+        <f>IF(T4=0,"",AC4/T4)</f>
+        <v/>
+      </c>
+      <c r="AE4" s="36">
+        <f>IF(AC4&lt;=0,"",VLOOKUP(B4,country_opex,7,FALSE)/AC4)</f>
+        <v/>
+      </c>
+      <c r="AF4" s="33">
+        <f>((D4*O4/diesel_nmpg)*diesel_co2pg-(battery/range_nm)*D4*O4*VLOOKUP(B4,country_opex,4,FALSE))/1000</f>
+        <v/>
+      </c>
+      <c r="AG4" s="31" t="n">
+        <v>7693</v>
+      </c>
+      <c r="AH4" s="32" t="inlineStr">
+        <is>
+          <t>T5</t>
+        </is>
+      </c>
+      <c r="AI4" s="32" t="inlineStr">
+        <is>
+          <t>med</t>
+        </is>
+      </c>
+      <c r="AJ4" s="39" t="n">
+        <v>0.9</v>
+      </c>
+      <c r="AK4" s="34">
+        <f>IF(AG4="","",AG4*AJ4)</f>
+        <v/>
+      </c>
+      <c r="AL4" s="34">
+        <f>IF(OR(AG4="",R4=0),"",MIN(IF(AT4="",9.9E+99,AT4),FLOOR(AK4/R4,1)))</f>
+        <v/>
+      </c>
+      <c r="AM4" s="38">
+        <f>IF(AL4="","",AL4*T4)</f>
+        <v/>
+      </c>
+      <c r="AN4" s="36">
+        <f>IF(OR(AG4="",R4=0),"",MIN(IF(AT4="",9.9E+99,AT4),AK4/R4))</f>
+        <v/>
+      </c>
+      <c r="AO4" s="38">
+        <f>IF(AN4="","",AN4*T4)</f>
+        <v/>
+      </c>
+      <c r="AP4" s="40" t="n"/>
+      <c r="AQ4" s="32" t="inlineStr">
+        <is>
+          <t>Grounded</t>
+        </is>
+      </c>
+      <c r="AR4" s="41" t="n"/>
+      <c r="AS4" s="41" t="n"/>
+      <c r="AT4" s="42" t="n">
+        <v>5</v>
+      </c>
+      <c r="AU4" s="43">
+        <f>IF(((S4*pax_cap*load_thin*ROUND(K4*L4*revleg_thin,0))-(((battery/range_nm)*D4*ROUND(K4*L4*revleg_thin,0)*VLOOKUP(B4,country_opex,3,FALSE))+V4+W4+X4+Y4+Z4))&lt;=0,"",VLOOKUP(B4,country_opex,7,FALSE)/((S4*pax_cap*load_thin*ROUND(K4*L4*revleg_thin,0))-(((battery/range_nm)*D4*ROUND(K4*L4*revleg_thin,0)*VLOOKUP(B4,country_opex,3,FALSE))+V4+W4+X4+Y4+Z4)))</f>
+        <v/>
+      </c>
+      <c r="AV4" s="43">
+        <f>IF(((S4*pax_cap*load_mid*ROUND(K4*L4*revleg_mid,0))-(((battery/range_nm)*D4*ROUND(K4*L4*revleg_mid,0)*VLOOKUP(B4,country_opex,3,FALSE))+V4+W4+X4+Y4+Z4))&lt;=0,"",VLOOKUP(B4,country_opex,7,FALSE)/((S4*pax_cap*load_mid*ROUND(K4*L4*revleg_mid,0))-(((battery/range_nm)*D4*ROUND(K4*L4*revleg_mid,0)*VLOOKUP(B4,country_opex,3,FALSE))+V4+W4+X4+Y4+Z4)))</f>
+        <v/>
+      </c>
+      <c r="AW4" s="43">
+        <f>IF(((S4*pax_cap*load_full*ROUND(K4*L4*revleg_full,0))-(((battery/range_nm)*D4*ROUND(K4*L4*revleg_full,0)*VLOOKUP(B4,country_opex,3,FALSE))+V4+W4+X4+Y4+Z4))&lt;=0,"",VLOOKUP(B4,country_opex,7,FALSE)/((S4*pax_cap*load_full*ROUND(K4*L4*revleg_full,0))-(((battery/range_nm)*D4*ROUND(K4*L4*revleg_full,0)*VLOOKUP(B4,country_opex,3,FALSE))+V4+W4+X4+Y4+Z4)))</f>
+        <v/>
+      </c>
+      <c r="AX4" s="44" t="inlineStr">
+        <is>
+          <t>immaldives.com Maldives transfer costs (May 2026): shared speedboat $100-490 RT pp (=$50-245 OW); shared seaplane $400-820 RT pp (=$200-410 OW). atolltransfer.com scheduled $30-195 OW. Navier premium per-seat anchored between local premium speedboat and the seaplane the resort otherwise charges (R-MALDIVES-1).</t>
+        </is>
+      </c>
+      <c r="AY4" s="44" t="inlineStr">
+        <is>
+          <t>Modeled arrivals = published keys x occupancy 0.70 (Maldives Min. of Tourism avg) x (365/6.5 nights avg stay) x 1.9 pax/room. Inbound one-way transfers. T5-modeled/med; keys T1 resort-published. NULL for pure inter-resort excursion legs (R2).</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="29" t="inlineStr">
+        <is>
+          <t>Four Seasons</t>
+        </is>
+      </c>
+      <c r="B5" s="29" t="inlineStr">
+        <is>
+          <t>Maldives</t>
+        </is>
+      </c>
+      <c r="C5" s="30" t="inlineStr">
+        <is>
+          <t>Soneva Fushi (Kunfunadhoo, Baa) → Four Seasons Landaa Giraavaru (Baa)</t>
+        </is>
+      </c>
+      <c r="D5" s="31" t="n">
+        <v>11.7</v>
+      </c>
+      <c r="E5" s="26" t="n">
+        <v>175</v>
+      </c>
+      <c r="F5" s="32" t="inlineStr">
+        <is>
+          <t>T3</t>
+        </is>
+      </c>
+      <c r="G5" s="32" t="inlineStr">
+        <is>
+          <t>med</t>
+        </is>
+      </c>
+      <c r="H5" s="19" t="n">
+        <v>1</v>
+      </c>
+      <c r="I5" s="33">
+        <f>60*D5/cruise_kt</f>
+        <v/>
+      </c>
+      <c r="J5" s="33">
+        <f>I5+turn_min+dwell_min</f>
+        <v/>
+      </c>
+      <c r="K5" s="34">
+        <f>MIN(15,FLOOR(60*service_hr/J5,1))</f>
+        <v/>
+      </c>
+      <c r="L5" s="34">
+        <f>ROUND(365*mech_uptime*H5,0)</f>
+        <v/>
+      </c>
+      <c r="M5" s="35">
+        <f>mech_uptime</f>
+        <v/>
+      </c>
+      <c r="N5" s="35">
+        <f>revleg_sel</f>
+        <v/>
+      </c>
+      <c r="O5" s="34">
+        <f>ROUND(K5*L5*revleg_sel,0)</f>
+        <v/>
+      </c>
+      <c r="P5" s="36">
+        <f>load_sel</f>
+        <v/>
+      </c>
+      <c r="Q5" s="36">
+        <f>pax_cap*P5</f>
+        <v/>
+      </c>
+      <c r="R5" s="34">
+        <f>Q5*O5</f>
+        <v/>
+      </c>
+      <c r="S5" s="37">
+        <f>E5*discount</f>
+        <v/>
+      </c>
+      <c r="T5" s="38">
+        <f>S5*R5</f>
+        <v/>
+      </c>
+      <c r="U5" s="38">
+        <f>(battery/range_nm)*D5*O5*VLOOKUP(B5,country_opex,3,FALSE)</f>
+        <v/>
+      </c>
+      <c r="V5" s="38">
+        <f>VLOOKUP(B5,country_opex,2,FALSE)*crew_factor</f>
+        <v/>
+      </c>
+      <c r="W5" s="38">
+        <f>VLOOKUP(B5,country_opex,5,FALSE)</f>
+        <v/>
+      </c>
+      <c r="X5" s="38">
+        <f>maint</f>
+        <v/>
+      </c>
+      <c r="Y5" s="38">
+        <f>VLOOKUP(B5,country_opex,7,FALSE)*ins_pct</f>
+        <v/>
+      </c>
+      <c r="Z5" s="38">
+        <f>charge_berth</f>
+        <v/>
+      </c>
+      <c r="AA5" s="38">
+        <f>U5+V5+W5+X5+Y5+Z5</f>
+        <v/>
+      </c>
+      <c r="AB5" s="38">
+        <f>VLOOKUP(B5,country_opex,7,FALSE)/dep_years</f>
+        <v/>
+      </c>
+      <c r="AC5" s="38">
+        <f>T5-AA5</f>
+        <v/>
+      </c>
+      <c r="AD5" s="35">
+        <f>IF(T5=0,"",AC5/T5)</f>
+        <v/>
+      </c>
+      <c r="AE5" s="36">
+        <f>IF(AC5&lt;=0,"",VLOOKUP(B5,country_opex,7,FALSE)/AC5)</f>
+        <v/>
+      </c>
+      <c r="AF5" s="33">
+        <f>((D5*O5/diesel_nmpg)*diesel_co2pg-(battery/range_nm)*D5*O5*VLOOKUP(B5,country_opex,4,FALSE))/1000</f>
+        <v/>
+      </c>
+      <c r="AG5" s="31" t="n"/>
+      <c r="AH5" s="32" t="n"/>
+      <c r="AI5" s="32" t="inlineStr">
+        <is>
+          <t>null</t>
+        </is>
+      </c>
+      <c r="AJ5" s="39" t="n">
+        <v>0.9</v>
+      </c>
+      <c r="AK5" s="34">
+        <f>IF(AG5="","",AG5*AJ5)</f>
+        <v/>
+      </c>
+      <c r="AL5" s="34">
+        <f>IF(OR(AG5="",R5=0),"",MIN(IF(AT5="",9.9E+99,AT5),FLOOR(AK5/R5,1)))</f>
+        <v/>
+      </c>
+      <c r="AM5" s="38">
+        <f>IF(AL5="","",AL5*T5)</f>
+        <v/>
+      </c>
+      <c r="AN5" s="36">
+        <f>IF(OR(AG5="",R5=0),"",MIN(IF(AT5="",9.9E+99,AT5),AK5/R5))</f>
+        <v/>
+      </c>
+      <c r="AO5" s="38">
+        <f>IF(AN5="","",AN5*T5)</f>
+        <v/>
+      </c>
+      <c r="AP5" s="40" t="n"/>
+      <c r="AQ5" s="32" t="inlineStr">
+        <is>
+          <t>Estimated</t>
+        </is>
+      </c>
+      <c r="AR5" s="41" t="n"/>
+      <c r="AS5" s="41" t="n"/>
+      <c r="AT5" s="42" t="n"/>
+      <c r="AU5" s="43">
+        <f>IF(((S5*pax_cap*load_thin*ROUND(K5*L5*revleg_thin,0))-(((battery/range_nm)*D5*ROUND(K5*L5*revleg_thin,0)*VLOOKUP(B5,country_opex,3,FALSE))+V5+W5+X5+Y5+Z5))&lt;=0,"",VLOOKUP(B5,country_opex,7,FALSE)/((S5*pax_cap*load_thin*ROUND(K5*L5*revleg_thin,0))-(((battery/range_nm)*D5*ROUND(K5*L5*revleg_thin,0)*VLOOKUP(B5,country_opex,3,FALSE))+V5+W5+X5+Y5+Z5)))</f>
+        <v/>
+      </c>
+      <c r="AV5" s="43">
+        <f>IF(((S5*pax_cap*load_mid*ROUND(K5*L5*revleg_mid,0))-(((battery/range_nm)*D5*ROUND(K5*L5*revleg_mid,0)*VLOOKUP(B5,country_opex,3,FALSE))+V5+W5+X5+Y5+Z5))&lt;=0,"",VLOOKUP(B5,country_opex,7,FALSE)/((S5*pax_cap*load_mid*ROUND(K5*L5*revleg_mid,0))-(((battery/range_nm)*D5*ROUND(K5*L5*revleg_mid,0)*VLOOKUP(B5,country_opex,3,FALSE))+V5+W5+X5+Y5+Z5)))</f>
+        <v/>
+      </c>
+      <c r="AW5" s="43">
+        <f>IF(((S5*pax_cap*load_full*ROUND(K5*L5*revleg_full,0))-(((battery/range_nm)*D5*ROUND(K5*L5*revleg_full,0)*VLOOKUP(B5,country_opex,3,FALSE))+V5+W5+X5+Y5+Z5))&lt;=0,"",VLOOKUP(B5,country_opex,7,FALSE)/((S5*pax_cap*load_full*ROUND(K5*L5*revleg_full,0))-(((battery/range_nm)*D5*ROUND(K5*L5*revleg_full,0)*VLOOKUP(B5,country_opex,3,FALSE))+V5+W5+X5+Y5+Z5)))</f>
+        <v/>
+      </c>
+      <c r="AX5" s="44" t="inlineStr">
+        <is>
+          <t>immaldives.com Maldives transfer costs (May 2026): shared speedboat $100-490 RT pp (=$50-245 OW); shared seaplane $400-820 RT pp (=$200-410 OW). atolltransfer.com scheduled $30-195 OW. Navier premium per-seat anchored between local premium speedboat and the seaplane the resort otherwise charges (R-MALDIVES-1).</t>
+        </is>
+      </c>
+      <c r="AY5" s="44" t="inlineStr">
+        <is>
+          <t>NULL — pure inter-resort island-hop; no grounded crossing pool (R2). Geometry only.</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="45" t="inlineStr">
         <is>
           <t>TOTAL / median</t>
         </is>
       </c>
-      <c r="T4" s="27">
-        <f>SUM(T4:T3)</f>
-        <v/>
-      </c>
-      <c r="AC4" s="27">
-        <f>SUM(AC4:AC3)</f>
-        <v/>
-      </c>
-      <c r="AD4" s="28">
-        <f>IF(T4=0,"",AC4/T4)</f>
-        <v/>
-      </c>
-      <c r="AL4" s="29">
-        <f>SUM(AL4:AL3)</f>
-        <v/>
-      </c>
-      <c r="AM4" s="27">
-        <f>SUM(AM4:AM3)</f>
-        <v/>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" s="8" t="inlineStr">
+      <c r="T6" s="46">
+        <f>SUM(T4:T5)</f>
+        <v/>
+      </c>
+      <c r="AC6" s="46">
+        <f>SUM(AC4:AC5)</f>
+        <v/>
+      </c>
+      <c r="AD6" s="47">
+        <f>IF(T6=0,"",AC6/T6)</f>
+        <v/>
+      </c>
+      <c r="AL6" s="48">
+        <f>SUM(AL4:AL5)</f>
+        <v/>
+      </c>
+      <c r="AM6" s="46">
+        <f>SUM(AM4:AM5)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="8" t="inlineStr">
         <is>
           <t>Market fleet build-up — grounded floor (network-sum of raw vessel fractions per market, rounded once; subset slices excluded; legacy per-corridor-floor totals above kept for reference)</t>
         </is>
       </c>
     </row>
-    <row r="7">
-      <c r="A7" s="24" t="inlineStr">
+    <row r="9">
+      <c r="A9" s="24" t="inlineStr">
         <is>
           <t>Market</t>
         </is>
       </c>
-      <c r="B7" s="24" t="inlineStr">
+      <c r="B9" s="24" t="inlineStr">
         <is>
           <t>Fleet basis</t>
         </is>
       </c>
-      <c r="C7" s="24" t="inlineStr">
+      <c r="C9" s="24" t="inlineStr">
         <is>
           <t>Raw vessels (sum)</t>
         </is>
       </c>
-      <c r="D7" s="24" t="inlineStr">
+      <c r="D9" s="24" t="inlineStr">
         <is>
           <t>Fleet (rounded once)</t>
         </is>
       </c>
-      <c r="E7" s="24" t="inlineStr">
+      <c r="E9" s="24" t="inlineStr">
         <is>
           <t>Market rev/yr (raw sum)</t>
         </is>
       </c>
     </row>
-    <row r="8">
-      <c r="A8" s="26" t="inlineStr">
+    <row r="10">
+      <c r="A10" s="25" t="inlineStr">
+        <is>
+          <t>Four Seasons</t>
+        </is>
+      </c>
+      <c r="B10" s="13" t="inlineStr">
+        <is>
+          <t>network_sum / ceil</t>
+        </is>
+      </c>
+      <c r="C10" s="23">
+        <f>SUMIFS(AN4:AN5,A4:A5,"Four Seasons",AP4:AP5,"=",AQ4:AQ5,"Grounded")</f>
+        <v/>
+      </c>
+      <c r="D10" s="49">
+        <f>IF(C10=0,0,CEILING(C10,1))</f>
+        <v/>
+      </c>
+      <c r="E10" s="50">
+        <f>SUMIFS(AO4:AO5,A4:A5,"Four Seasons",AP4:AP5,"=",AQ4:AQ5,"Grounded")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="45" t="inlineStr">
         <is>
           <t>GROUNDED FLOOR (PUBLISHED)</t>
         </is>
       </c>
-      <c r="D8" s="29">
-        <f>SUM(D8:D7)</f>
-        <v/>
-      </c>
-      <c r="E8" s="27">
-        <f>SUM(E8:E7)</f>
+      <c r="D11" s="48">
+        <f>SUM(D10:D10)</f>
+        <v/>
+      </c>
+      <c r="E11" s="46">
+        <f>SUM(E10:E10)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="20" t="inlineStr">
+        <is>
+          <t>ESTIMATED DEMAND (country-median cascade; held OUT of grounded floor)</t>
+        </is>
+      </c>
+      <c r="D12" s="51">
+        <f>SUMIF(AQ4:AQ5,"Estimated",AL4:AL5)</f>
+        <v/>
+      </c>
+      <c r="E12" s="52">
+        <f>SUMIF(AQ4:AQ5,"Estimated",AM4:AM5)</f>
         <v/>
       </c>
     </row>
   </sheetData>
   <mergeCells count="2">
-    <mergeCell ref="A6:L6"/>
+    <mergeCell ref="A8:L8"/>
     <mergeCell ref="A1:L1"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -2269,7 +2814,7 @@
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="30" t="inlineStr">
+      <c r="A5" s="25" t="inlineStr">
         <is>
           <t>Induced demand (k)</t>
         </is>
@@ -2290,19 +2835,19 @@
       </c>
     </row>
     <row r="6">
-      <c r="A6" s="30" t="inlineStr">
+      <c r="A6" s="25" t="inlineStr">
         <is>
           <t>Mature capture rate (c)</t>
         </is>
       </c>
-      <c r="B6" s="31" t="n">
-        <v>0.15</v>
-      </c>
-      <c r="C6" s="31" t="n">
-        <v>0.25</v>
-      </c>
-      <c r="D6" s="31" t="n">
-        <v>0.4</v>
+      <c r="B6" s="39" t="n">
+        <v>0.9</v>
+      </c>
+      <c r="C6" s="39" t="n">
+        <v>0.9</v>
+      </c>
+      <c r="D6" s="39" t="n">
+        <v>0.95</v>
       </c>
       <c r="E6" s="14" t="inlineStr">
         <is>
@@ -2311,7 +2856,7 @@
       </c>
     </row>
     <row r="7">
-      <c r="A7" s="30" t="inlineStr">
+      <c r="A7" s="25" t="inlineStr">
         <is>
           <t>Journey GMV multiple (m)</t>
         </is>
@@ -2332,7 +2877,7 @@
       </c>
     </row>
     <row r="8">
-      <c r="A8" s="30" t="inlineStr">
+      <c r="A8" s="25" t="inlineStr">
         <is>
           <t>Greenfield network factor (g)</t>
         </is>
@@ -2353,12 +2898,12 @@
       </c>
     </row>
     <row r="9">
-      <c r="A9" s="30" t="inlineStr">
+      <c r="A9" s="25" t="inlineStr">
         <is>
           <t>Platform take rate</t>
         </is>
       </c>
-      <c r="C9" s="31" t="n">
+      <c r="C9" s="39" t="n">
         <v>0.18</v>
       </c>
       <c r="E9" s="14" t="inlineStr">
@@ -2368,17 +2913,17 @@
       </c>
     </row>
     <row r="11">
-      <c r="A11" s="30" t="inlineStr">
+      <c r="A11" s="25" t="inlineStr">
         <is>
           <t>SOM capture rate (floor)</t>
         </is>
       </c>
-      <c r="C11" s="31" t="n">
-        <v>0.1</v>
+      <c r="C11" s="39" t="n">
+        <v>0.9</v>
       </c>
       <c r="E11" s="14" t="inlineStr">
         <is>
-          <t>New-entrant ~10% share of today's pool (= the published floor).</t>
+          <t>Captive sole-operator capture (~90%) that builds the published floor; M_today = floor ÷ this = the true corridor spend pool.</t>
         </is>
       </c>
     </row>
@@ -2417,28 +2962,28 @@
       </c>
     </row>
     <row r="15">
-      <c r="A15" s="30" t="inlineStr">
+      <c r="A15" s="25" t="inlineStr">
         <is>
           <t>SOM floor — Navier transport rev/yr (PUBLISHED)</t>
         </is>
       </c>
-      <c r="C15" s="32">
+      <c r="C15" s="50">
         <f>som_floor_rev</f>
         <v/>
       </c>
       <c r="E15" s="14" t="inlineStr">
         <is>
-          <t>Live sum of grounded corridor market-rev (10% capture, today's demand, sourced corridors).</t>
+          <t>Live sum of grounded-floor corridor market-rev only (Floor bucket = Grounded; cascade-estimated rows held out). Matches growth.py _headline_anchor and deck TAM.</t>
         </is>
       </c>
     </row>
     <row r="16">
-      <c r="A16" s="30" t="inlineStr">
+      <c r="A16" s="25" t="inlineStr">
         <is>
           <t>M_today — full transport spend on sourced corridors</t>
         </is>
       </c>
-      <c r="C16" s="32">
+      <c r="C16" s="50">
         <f>$C$15/$C$11</f>
         <v/>
       </c>
@@ -2449,44 +2994,44 @@
       </c>
     </row>
     <row r="18">
-      <c r="A18" s="30" t="inlineStr">
-        <is>
-          <t>SOM full network (~10% capture, today, +greenfield)</t>
-        </is>
-      </c>
-      <c r="B18" s="32">
+      <c r="A18" s="25" t="inlineStr">
+        <is>
+          <t>SOM full network (~90% capture, today, +greenfield)</t>
+        </is>
+      </c>
+      <c r="B18" s="50">
         <f>$C$16*$C$11*$B$8</f>
         <v/>
       </c>
-      <c r="C18" s="32">
+      <c r="C18" s="50">
         <f>$C$16*$C$11*$C$8</f>
         <v/>
       </c>
-      <c r="D18" s="32">
+      <c r="D18" s="50">
         <f>$C$16*$C$11*$D$8</f>
         <v/>
       </c>
       <c r="E18" s="14" t="inlineStr">
         <is>
-          <t>Floor posture (~10% captive capture, today's demand) extended across the whole mapped network.</t>
+          <t>Floor posture (~90% captive capture, today's demand) extended across the whole mapped network.</t>
         </is>
       </c>
     </row>
     <row r="19">
-      <c r="A19" s="30" t="inlineStr">
+      <c r="A19" s="25" t="inlineStr">
         <is>
           <t>SAM — sourced corridors only (depth, no greenfield)</t>
         </is>
       </c>
-      <c r="B19" s="32">
+      <c r="B19" s="50">
         <f>$C$16*$B$5*$B$6</f>
         <v/>
       </c>
-      <c r="C19" s="32">
+      <c r="C19" s="50">
         <f>$C$16*$C$5*$C$6</f>
         <v/>
       </c>
-      <c r="D19" s="32">
+      <c r="D19" s="50">
         <f>$C$16*$D$5*$D$6</f>
         <v/>
       </c>
@@ -2497,20 +3042,20 @@
       </c>
     </row>
     <row r="20">
-      <c r="A20" s="30" t="inlineStr">
+      <c r="A20" s="25" t="inlineStr">
         <is>
           <t>SAM — Navier transport rev @ full network (HEADLINE)</t>
         </is>
       </c>
-      <c r="B20" s="32">
+      <c r="B20" s="50">
         <f>$C$16*$B$5*$B$6*$B$8</f>
         <v/>
       </c>
-      <c r="C20" s="32">
+      <c r="C20" s="50">
         <f>$C$16*$C$5*$C$6*$C$8</f>
         <v/>
       </c>
-      <c r="D20" s="32">
+      <c r="D20" s="50">
         <f>$C$16*$D$5*$D$6*$D$8</f>
         <v/>
       </c>
@@ -2521,20 +3066,20 @@
       </c>
     </row>
     <row r="21">
-      <c r="A21" s="30" t="inlineStr">
+      <c r="A21" s="25" t="inlineStr">
         <is>
           <t>Marine mobility TAM — induced marine-transfer market (LB-110)</t>
         </is>
       </c>
-      <c r="B21" s="32">
+      <c r="B21" s="50">
         <f>$C$16*$B$5*$B$8</f>
         <v/>
       </c>
-      <c r="C21" s="32">
+      <c r="C21" s="50">
         <f>$C$16*$C$5*$C$8</f>
         <v/>
       </c>
-      <c r="D21" s="32">
+      <c r="D21" s="50">
         <f>$C$16*$D$5*$D$8</f>
         <v/>
       </c>
@@ -2545,20 +3090,20 @@
       </c>
     </row>
     <row r="22">
-      <c r="A22" s="30" t="inlineStr">
+      <c r="A22" s="25" t="inlineStr">
         <is>
           <t>Journey GMV — induced crossing × multiple (was TAM journey GMV)</t>
         </is>
       </c>
-      <c r="B22" s="32">
+      <c r="B22" s="50">
         <f>$C$16*$B$5*$B$7*$B$8</f>
         <v/>
       </c>
-      <c r="C22" s="32">
+      <c r="C22" s="50">
         <f>$C$16*$C$5*$C$7*$C$8</f>
         <v/>
       </c>
-      <c r="D22" s="32">
+      <c r="D22" s="50">
         <f>$C$16*$D$5*$D$7*$D$8</f>
         <v/>
       </c>
@@ -2569,20 +3114,20 @@
       </c>
     </row>
     <row r="23">
-      <c r="A23" s="30" t="inlineStr">
+      <c r="A23" s="25" t="inlineStr">
         <is>
           <t>Journey GMV routed through Navier network</t>
         </is>
       </c>
-      <c r="B23" s="32">
+      <c r="B23" s="50">
         <f>$C$16*$B$5*$B$6*$B$7*$B$8</f>
         <v/>
       </c>
-      <c r="C23" s="32">
+      <c r="C23" s="50">
         <f>$C$16*$C$5*$C$6*$C$7*$C$8</f>
         <v/>
       </c>
-      <c r="D23" s="32">
+      <c r="D23" s="50">
         <f>$C$16*$D$5*$D$6*$D$7*$D$8</f>
         <v/>
       </c>
@@ -2593,20 +3138,20 @@
       </c>
     </row>
     <row r="24">
-      <c r="A24" s="30" t="inlineStr">
+      <c r="A24" s="25" t="inlineStr">
         <is>
           <t>Partner platform revenue on Navier (LB-113 — on-Navier subset, not 18% of full Journey GMV)</t>
         </is>
       </c>
-      <c r="B24" s="32">
+      <c r="B24" s="50">
         <f>$C$16*$B$5*$B$6*$B$7*$B$8*$C$9</f>
         <v/>
       </c>
-      <c r="C24" s="32">
+      <c r="C24" s="50">
         <f>$C$16*$C$5*$C$6*$C$7*$C$8*$C$9</f>
         <v/>
       </c>
-      <c r="D24" s="32">
+      <c r="D24" s="50">
         <f>$C$16*$D$5*$D$6*$D$7*$D$8*$C$9</f>
         <v/>
       </c>
@@ -2617,12 +3162,12 @@
       </c>
     </row>
     <row r="26">
-      <c r="A26" s="33" t="inlineStr">
+      <c r="A26" s="53" t="inlineStr">
         <is>
           <t>Note</t>
         </is>
       </c>
-      <c r="B26" s="34" t="inlineStr">
+      <c r="B26" s="54" t="inlineStr">
         <is>
           <t>All rungs are one multiplication chain off M_today, which is live off the corridor floor. Change any input (a fare, a multiplier, the scenario) and the whole ladder moves. Bands (low/MID/high) are never single points; greenfield census is per-partner.</t>
         </is>
